--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PERSONALHOME ADESAVI.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PERSONALHOME ADESAVI.xlsx
@@ -565,13 +565,13 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>18.6626</v>
+        <v>12.7929</v>
       </c>
       <c r="E2" t="n">
-        <v>28.8931</v>
+        <v>22.0998</v>
       </c>
       <c r="F2" t="n">
-        <v>-10.2305</v>
+        <v>-9.306799999999999</v>
       </c>
       <c r="G2" t="n">
         <v>-10.4578</v>
@@ -610,13 +610,13 @@
         <v>57.1761</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.2277</v>
+        <v>-8.097299999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>5.5924</v>
+        <v>-1.2012</v>
       </c>
       <c r="U2" t="n">
-        <v>-7.8202</v>
+        <v>-6.896</v>
       </c>
       <c r="V2" t="n">
         <v>13.4212</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SERNEGUET GARVI</t>
+          <t>P. LOPEZ-VALVERDE CARRASCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>6.560199999999999</v>
+        <v>5.651200000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>22.4356</v>
+        <v>0.8826000000000005</v>
       </c>
       <c r="F3" t="n">
-        <v>-15.8756</v>
+        <v>4.7687</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.269899999999998</v>
+        <v>-6.808400000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5890999999999993</v>
+        <v>-9.347900000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6809999999999995</v>
+        <v>2.5395</v>
       </c>
       <c r="J3" t="n">
-        <v>41.8533</v>
+        <v>28.5793</v>
       </c>
       <c r="K3" t="n">
-        <v>29.8174</v>
+        <v>16.2438</v>
       </c>
       <c r="L3" t="n">
-        <v>12.0359</v>
+        <v>12.3353</v>
       </c>
       <c r="M3" t="n">
-        <v>-43.1234</v>
+        <v>-35.3878</v>
       </c>
       <c r="N3" t="n">
-        <v>-30.4061</v>
+        <v>-25.5919</v>
       </c>
       <c r="O3" t="n">
-        <v>-12.7171</v>
+        <v>-9.795999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-15.6621</v>
+        <v>27.7389</v>
       </c>
       <c r="Q3" t="n">
-        <v>-78.3105</v>
+        <v>-33.966</v>
       </c>
       <c r="R3" t="n">
-        <v>62.6484</v>
+        <v>61.7049</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1574</v>
+        <v>-7.412199999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-3.2706</v>
+        <v>-3.2197</v>
       </c>
       <c r="U3" t="n">
-        <v>2.113</v>
+        <v>-4.192200000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>24.6495</v>
+        <v>-7.8672</v>
       </c>
       <c r="W3" t="n">
-        <v>62.1629</v>
+        <v>9.488800000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>-37.5134</v>
+        <v>-17.3561</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. LOPEZ-VALVERDE CARRASCO</t>
+          <t>A. SERNEGUET GARVI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>6.386600000000001</v>
+        <v>0.330899999999998</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7583999999999991</v>
+        <v>21.6256</v>
       </c>
       <c r="F4" t="n">
-        <v>5.628</v>
+        <v>-21.2948</v>
       </c>
       <c r="G4" t="n">
-        <v>-6.808400000000001</v>
+        <v>-1.269899999999998</v>
       </c>
       <c r="H4" t="n">
-        <v>-9.347900000000001</v>
+        <v>-0.5890999999999993</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5395</v>
+        <v>-0.6809999999999995</v>
       </c>
       <c r="J4" t="n">
-        <v>28.5793</v>
+        <v>41.8533</v>
       </c>
       <c r="K4" t="n">
-        <v>16.2438</v>
+        <v>29.8174</v>
       </c>
       <c r="L4" t="n">
-        <v>12.3353</v>
+        <v>12.0359</v>
       </c>
       <c r="M4" t="n">
-        <v>-35.3878</v>
+        <v>-43.1234</v>
       </c>
       <c r="N4" t="n">
-        <v>-25.5919</v>
+        <v>-30.4061</v>
       </c>
       <c r="O4" t="n">
-        <v>-9.795999999999999</v>
+        <v>-12.7171</v>
       </c>
       <c r="P4" t="n">
-        <v>27.7389</v>
+        <v>-15.6621</v>
       </c>
       <c r="Q4" t="n">
-        <v>-33.966</v>
+        <v>-78.3105</v>
       </c>
       <c r="R4" t="n">
-        <v>61.7049</v>
+        <v>62.6484</v>
       </c>
       <c r="S4" t="n">
-        <v>-6.676400000000001</v>
+        <v>-7.3866</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.343900000000001</v>
+        <v>-4.0805</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.3328</v>
+        <v>-3.306</v>
       </c>
       <c r="V4" t="n">
-        <v>-7.8672</v>
+        <v>24.6495</v>
       </c>
       <c r="W4" t="n">
-        <v>9.488800000000001</v>
+        <v>62.1629</v>
       </c>
       <c r="X4" t="n">
-        <v>-17.3561</v>
+        <v>-37.5134</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GARCIA PEIDRO</t>
+          <t>N. ALBALADEJO PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2113</v>
+        <v>0.2146999999999988</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-9.794700000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2113</v>
+        <v>10.0097</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2113</v>
+        <v>-2.2931</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2113</v>
+        <v>6.8764</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-9.169499999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>13.6079</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>17.8919</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-4.283899999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2113</v>
+        <v>-15.9012</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2113</v>
+        <v>-11.0156</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-4.8857</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>10.3785</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-28.1163</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>38.4948</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-8.2217</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-3.6062</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-4.615699999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3511999999999997</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>8.319599999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-7.968500000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. FERRISI</t>
+          <t>J. GARCIA PEIDRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,61 +952,61 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3562000000000001</v>
+        <v>-0.2113</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3021</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6583</v>
+        <v>-0.2113</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3262</v>
+        <v>-0.2113</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4281</v>
+        <v>-0.2113</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1018</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5248</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4014</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1234</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8512</v>
+        <v>-0.2113</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8296</v>
+        <v>-0.2113</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.02160000000000001</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5961000000000001</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2229</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3733</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. POPOVIC</t>
+          <t>M. FERRISI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3471</v>
+        <v>-0.2852</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9075</v>
+        <v>0.3995</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4396</v>
+        <v>-0.6847</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4804</v>
+        <v>-0.3262</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7418</v>
+        <v>-0.4281</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7385</v>
+        <v>0.1018</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1997</v>
+        <v>0.5248</v>
       </c>
       <c r="K8" t="n">
-        <v>0.803</v>
+        <v>0.4014</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.0027</v>
+        <v>0.1234</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2807</v>
+        <v>-0.8512</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5449</v>
+        <v>-0.8296</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7359</v>
+        <v>-0.02160000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4531</v>
+        <v>0.5661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7611999999999999</v>
+        <v>-0.5252</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5756</v>
+        <v>-0.1254</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1857</v>
+        <v>-0.3996999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4263</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LAVRENOV</t>
+          <t>S. GALVEZ ARROYO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7013</v>
+        <v>-1.013499999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4002</v>
+        <v>6.456900000000003</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1015</v>
+        <v>-7.4707</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6029</v>
+        <v>11.5518</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.00550000000000006</v>
+        <v>18.1196</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5973999999999999</v>
+        <v>-6.567699999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6934</v>
+        <v>53.3098</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0354</v>
+        <v>50.1046</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6581</v>
+        <v>3.205099999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2963</v>
+        <v>-41.7584</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0409</v>
+        <v>-31.9856</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2555</v>
+        <v>-9.7728</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9434999999999999</v>
+        <v>-13.9638</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0757</v>
+        <v>-81.5184</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1322</v>
+        <v>67.55459999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.392</v>
+        <v>-16.2564</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7824</v>
+        <v>-6.764</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3903</v>
+        <v>-9.4922</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.547</v>
+        <v>17.655</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>41.4292</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.547</v>
+        <v>-23.7745</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. MILETIC</t>
+          <t>J. POPOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8586</v>
+        <v>-1.8418</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.9636</v>
+        <v>-1.3229</v>
       </c>
       <c r="F10" t="n">
-        <v>3.105</v>
+        <v>-0.5189</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.8971</v>
+        <v>-2.4804</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.879</v>
+        <v>-0.7418</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.018</v>
+        <v>-1.7385</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.480399999999999</v>
+        <v>-0.1997</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.7476</v>
+        <v>0.803</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.7328</v>
+        <v>-1.0027</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5833999999999999</v>
+        <v>-2.2807</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1315</v>
+        <v>-1.5449</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7148</v>
+        <v>-0.7359</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7548</v>
+        <v>1.3209</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2644</v>
+        <v>-1.1322</v>
       </c>
       <c r="R10" t="n">
-        <v>3.0192</v>
+        <v>2.4531</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8141999999999999</v>
+        <v>-0.2561</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6901999999999999</v>
+        <v>0.009100000000000004</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.124</v>
+        <v>-0.265</v>
       </c>
       <c r="V10" t="n">
-        <v>2.0979</v>
+        <v>-0.4263</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4714</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3736</v>
+        <v>-0.4263</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MADINYH EGEA</t>
+          <t>F. MILETIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3206</v>
+        <v>-2.6352</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7872000000000003</v>
+        <v>-5.846</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.1078</v>
+        <v>3.2109</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2625</v>
+        <v>-4.8971</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9587000000000001</v>
+        <v>-1.879</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6962999999999999</v>
+        <v>-3.018</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5527</v>
+        <v>-5.480399999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>3.0592</v>
+        <v>-1.7476</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4936</v>
+        <v>-3.7328</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.2901</v>
+        <v>0.5833999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.1004</v>
+        <v>-0.1315</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1898</v>
+        <v>0.7148</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9627</v>
+        <v>-2.2644</v>
       </c>
       <c r="R11" t="n">
-        <v>5.2836</v>
+        <v>3.0192</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2593</v>
+        <v>-0.5908</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9331999999999999</v>
+        <v>-0.5727</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1926</v>
+        <v>-0.0181</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.6448</v>
+        <v>2.0979</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2638</v>
+        <v>2.4714</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.9086</v>
+        <v>-0.3736</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. GONZALEZ ESPOSITO</t>
+          <t>A. LAVRENOV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4174</v>
+        <v>-2.8878</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9479</v>
+        <v>0.1078999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.4696</v>
+        <v>-2.9956</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6769</v>
+        <v>-0.6029</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8241000000000001</v>
+        <v>-0.00550000000000006</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8528</v>
+        <v>-0.5973999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0661</v>
+        <v>1.6934</v>
       </c>
       <c r="K12" t="n">
-        <v>1.4689</v>
+        <v>1.0354</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4028</v>
+        <v>0.6581</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.7431</v>
+        <v>-2.2963</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.293</v>
+        <v>-1.0409</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4501</v>
+        <v>-1.2555</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.9434999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1322</v>
+        <v>-2.0757</v>
       </c>
       <c r="R12" t="n">
         <v>1.1322</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.616</v>
+        <v>0.2055</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8818</v>
+        <v>0.4901</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7342</v>
+        <v>-0.2845</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1245</v>
+        <v>-1.547</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1245</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. RUIZ FRANCO</t>
+          <t>M. GONZALEZ ESPOSITO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.7008</v>
+        <v>-3.7573</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4417</v>
+        <v>-0.4994</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.259</v>
+        <v>-3.2579</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.1917</v>
+        <v>-2.6769</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.679</v>
+        <v>-0.8241000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-1.8528</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.5671</v>
+        <v>1.0661</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.7897</v>
+        <v>1.4689</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2226</v>
+        <v>-0.4028</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.6245</v>
+        <v>-3.7431</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.8893</v>
+        <v>-2.293</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7353999999999999</v>
+        <v>-1.4501</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.9062</v>
+        <v>-1.1322</v>
       </c>
       <c r="R13" t="n">
-        <v>4.9062</v>
+        <v>1.1322</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.264</v>
+        <v>-0.9558</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0314</v>
+        <v>-0.4333</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2954</v>
+        <v>-0.5225</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2452</v>
+        <v>-0.1245</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2452</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>V. MARTIN SORIANO</t>
+          <t>J. MADINYH EGEA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.9683</v>
+        <v>-5.061999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.0093</v>
+        <v>-0.1082000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9588</v>
+        <v>-4.9537</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.7472</v>
+        <v>0.2625</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7045</v>
+        <v>0.9587000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0427</v>
+        <v>-0.6962999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9211</v>
+        <v>3.5527</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.0033</v>
+        <v>3.0592</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0822</v>
+        <v>0.4936</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8262</v>
+        <v>-3.2901</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7013</v>
+        <v>-2.1004</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.125</v>
+        <v>-1.1898</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7548</v>
+        <v>1.3209</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2644</v>
+        <v>-3.9627</v>
       </c>
       <c r="R14" t="n">
-        <v>3.0192</v>
+        <v>5.2836</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8142</v>
+        <v>-1.0006</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4275</v>
+        <v>0.03790000000000007</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3868</v>
+        <v>-1.0386</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.1615</v>
+        <v>-5.6448</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6036</v>
+        <v>0.2638</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.7652</v>
+        <v>-5.9086</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. ALBALADEJO PEREZ</t>
+          <t>V. MARTIN SORIANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.242500000000001</v>
+        <v>-5.6027</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.8127</v>
+        <v>-3.0093</v>
       </c>
       <c r="F15" t="n">
-        <v>7.570600000000001</v>
+        <v>-2.5932</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.2931</v>
+        <v>-2.7472</v>
       </c>
       <c r="H15" t="n">
-        <v>6.8764</v>
+        <v>-1.7045</v>
       </c>
       <c r="I15" t="n">
-        <v>-9.169499999999999</v>
+        <v>-1.0427</v>
       </c>
       <c r="J15" t="n">
-        <v>13.6079</v>
+        <v>-0.9211</v>
       </c>
       <c r="K15" t="n">
-        <v>17.8919</v>
+        <v>-1.0033</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.283899999999999</v>
+        <v>0.0822</v>
       </c>
       <c r="M15" t="n">
-        <v>-15.9012</v>
+        <v>-1.8262</v>
       </c>
       <c r="N15" t="n">
-        <v>-11.0156</v>
+        <v>-0.7013</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.8857</v>
+        <v>-1.125</v>
       </c>
       <c r="P15" t="n">
-        <v>10.3785</v>
+        <v>0.7548</v>
       </c>
       <c r="Q15" t="n">
-        <v>-28.1163</v>
+        <v>-2.2644</v>
       </c>
       <c r="R15" t="n">
-        <v>38.4948</v>
+        <v>3.0192</v>
       </c>
       <c r="S15" t="n">
-        <v>-14.679</v>
+        <v>-0.4483999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.6246</v>
+        <v>-0.4275</v>
       </c>
       <c r="U15" t="n">
-        <v>-7.0549</v>
+        <v>-0.02099999999999994</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3511999999999997</v>
+        <v>-3.1615</v>
       </c>
       <c r="W15" t="n">
-        <v>8.319599999999999</v>
+        <v>0.6036</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.968500000000001</v>
+        <v>-3.7652</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ORTIN GOMEZ</t>
+          <t>D. RUIZ FRANCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>-10.8585</v>
+        <v>-6.097300000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5822999999999998</v>
+        <v>-5.4733</v>
       </c>
       <c r="F16" t="n">
-        <v>-10.2764</v>
+        <v>-0.624</v>
       </c>
       <c r="G16" t="n">
-        <v>-5.1013</v>
+        <v>-4.1917</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.6551</v>
+        <v>-3.679</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.4461</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3382</v>
+        <v>-1.5671</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3363</v>
+        <v>-1.7897</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.9981000000000002</v>
+        <v>0.2226</v>
       </c>
       <c r="M16" t="n">
-        <v>-9.4396</v>
+        <v>-2.6245</v>
       </c>
       <c r="N16" t="n">
-        <v>-7.9917</v>
+        <v>-1.8893</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4479</v>
+        <v>-0.7353999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>4.717499999999999</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-7.7367</v>
+        <v>-4.9062</v>
       </c>
       <c r="R16" t="n">
-        <v>12.4542</v>
+        <v>4.9062</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.331799999999999</v>
+        <v>-0.6607</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.7494</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>-4.5823</v>
+        <v>-1.6604</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.143</v>
+        <v>-1.2452</v>
       </c>
       <c r="W16" t="n">
-        <v>5.5654</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-8.708500000000001</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. GALVEZ ARROYO</t>
+          <t>A. ORTIN GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>-15.1731</v>
+        <v>-8.4238</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.2356</v>
+        <v>0.1400000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.9372</v>
+        <v>-8.5639</v>
       </c>
       <c r="G17" t="n">
-        <v>11.5518</v>
+        <v>-5.1013</v>
       </c>
       <c r="H17" t="n">
-        <v>18.1196</v>
+        <v>-2.6551</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.567699999999999</v>
+        <v>-2.4461</v>
       </c>
       <c r="J17" t="n">
-        <v>53.3098</v>
+        <v>4.3382</v>
       </c>
       <c r="K17" t="n">
-        <v>50.1046</v>
+        <v>5.3363</v>
       </c>
       <c r="L17" t="n">
-        <v>3.205099999999999</v>
+        <v>-0.9981000000000002</v>
       </c>
       <c r="M17" t="n">
-        <v>-41.7584</v>
+        <v>-9.4396</v>
       </c>
       <c r="N17" t="n">
-        <v>-31.9856</v>
+        <v>-7.9917</v>
       </c>
       <c r="O17" t="n">
-        <v>-9.7728</v>
+        <v>-1.4479</v>
       </c>
       <c r="P17" t="n">
-        <v>-13.9638</v>
+        <v>4.717499999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-81.5184</v>
+        <v>-7.7367</v>
       </c>
       <c r="R17" t="n">
-        <v>67.55459999999999</v>
+        <v>12.4542</v>
       </c>
       <c r="S17" t="n">
-        <v>-30.4158</v>
+        <v>-4.897</v>
       </c>
       <c r="T17" t="n">
-        <v>-16.4572</v>
+        <v>-2.0269</v>
       </c>
       <c r="U17" t="n">
-        <v>-13.9587</v>
+        <v>-2.8699</v>
       </c>
       <c r="V17" t="n">
-        <v>17.655</v>
+        <v>-3.143</v>
       </c>
       <c r="W17" t="n">
-        <v>41.4292</v>
+        <v>5.5654</v>
       </c>
       <c r="X17" t="n">
-        <v>-23.7745</v>
+        <v>-8.708500000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>-30.3088</v>
+        <v>-20.8704</v>
       </c>
       <c r="E18" t="n">
-        <v>-22.597</v>
+        <v>-18.9502</v>
       </c>
       <c r="F18" t="n">
-        <v>-7.7119</v>
+        <v>-1.9204</v>
       </c>
       <c r="G18" t="n">
         <v>-20.0113</v>
@@ -1858,13 +1858,13 @@
         <v>39.8157</v>
       </c>
       <c r="S18" t="n">
-        <v>-20.4393</v>
+        <v>-11.0005</v>
       </c>
       <c r="T18" t="n">
-        <v>-7.6499</v>
+        <v>-4.0029</v>
       </c>
       <c r="U18" t="n">
-        <v>-12.7894</v>
+        <v>-6.9977</v>
       </c>
       <c r="V18" t="n">
         <v>-1.746599999999999</v>
@@ -1891,13 +1891,13 @@
         <v>18</v>
       </c>
       <c r="D19" t="n">
-        <v>-39.1677</v>
+        <v>-39.3139</v>
       </c>
       <c r="E19" t="n">
-        <v>-19.4761</v>
+        <v>-20.8755</v>
       </c>
       <c r="F19" t="n">
-        <v>-19.6917</v>
+        <v>-18.4385</v>
       </c>
       <c r="G19" t="n">
         <v>-30.5034</v>
@@ -1936,13 +1936,13 @@
         <v>27.3615</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.5273</v>
+        <v>-2.6735</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3545000000000001</v>
+        <v>-1.7536</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.1732</v>
+        <v>-0.9198000000000003</v>
       </c>
       <c r="V19" t="n">
         <v>-15.0061</v>
@@ -1969,13 +1969,13 @@
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>-98.7058</v>
+        <v>-78.6955</v>
       </c>
       <c r="E20" t="n">
-        <v>-22.08010000000001</v>
+        <v>-13.8502</v>
       </c>
       <c r="F20" t="n">
-        <v>-76.62559999999999</v>
+        <v>-64.8451</v>
       </c>
       <c r="G20" t="n">
         <v>-82.44759999999999</v>
@@ -1993,7 +1993,7 @@
         <v>144.1341</v>
       </c>
       <c r="L20" t="n">
-        <v>23.3151</v>
+        <v>23.31509999999999</v>
       </c>
       <c r="M20" t="n">
         <v>-249.8973</v>
@@ -2014,13 +2014,13 @@
         <v>388.722</v>
       </c>
       <c r="S20" t="n">
-        <v>-90.18770000000001</v>
+        <v>-70.1773</v>
       </c>
       <c r="T20" t="n">
-        <v>-34.9087</v>
+        <v>-26.6768</v>
       </c>
       <c r="U20" t="n">
-        <v>-55.28080000000001</v>
+        <v>-43.49930000000001</v>
       </c>
       <c r="V20" t="n">
         <v>18.2626</v>
